--- a/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable. Maman dit : on mange ensemble, à table. Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
+          <t>C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable. On mange ensemble, à table. Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable.
+maman|On mange ensemble, à table.
+narrateur|Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Joséphine va manger. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Joséphine est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Joséphine boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Joséphine va manger. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Joséphine est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Joséphine boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joséphine s'assoit pour souper</t>
+          <t>La cuillère de bois</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les lampadaires s'allument. La cuillère en bois tape la casserole. Ça sent la soupe aux carottes. Mila s'assoit. On soupe ensemble, à table.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable. On mange ensemble, à table. Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
+          <t>Dehors, les lampadaires s'allument. La rue devient orange. Un chat passe sous la fenêtre. Dans la maison, ça sent la soupe. Une petite fumée monte. Elle va jusqu'à la vitre. La cuillère en bois tape la casserole. Toc. Toc. Mila vit ici, avec papa et maman. Son doudou attend sur une chaise. Le doudou a une oreille pliée. J'entends la cuillère ! Oui, Mila. La soupe est presque prête. Papa apporte les assiettes. Elles font un petit bruit. Le pain est dans le panier. Mila, viens. On va à table. Viens t'asseoir. Mila va vers sa chaise. Le carrelage est tiède, encore. Ça sent les carottes. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. La table est un peu chaude. Tu as vu la petite fumée ? Elle monte encore. La soupe sent les carottes. On attend un petit moment. Mila tient sa cuillère. Elle reste assise.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable.
-maman|On mange ensemble, à table.
-narrateur|Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Dehors, les lampadaires s'allument.
+narrateur|La rue devient orange.
+narrateur|Un chat passe sous la fenêtre.
+narrateur|Dans la maison, ça sent la soupe.
+narrateur|Une petite fumée monte.
+narrateur|Elle va jusqu'à la vitre.
+narrateur|La cuillère en bois tape la casserole.
+narrateur|Toc. Toc.
+narrateur|Mila vit ici, avec papa et maman.
+narrateur|Son doudou attend sur une chaise.
+narrateur|Le doudou a une oreille pliée.
+enfant-f|J'entends la cuillère !
+maman|Oui, Mila.
+maman|La soupe est presque prête.
+narrateur|Papa apporte les assiettes.
+narrateur|Elles font un petit bruit.
+narrateur|Le pain est dans le panier.
+papa|Mila, viens.
+papa|On va à table.
+maman|Viens t'asseoir.
+narrateur|Mila va vers sa chaise.
+narrateur|Le carrelage est tiède, encore.
+narrateur|Ça sent les carottes.
+narrateur|Elle tire un peu la chaise.
+narrateur|Elle s'assoit.
+narrateur|Elle pose les pieds par terre.
+papa|Bravo, Mila.
+papa|Tu es bien assise.
+narrateur|Papa s'assoit aussi.
+narrateur|Maman s'assoit près d'elle.
+maman|On est ensemble.
+maman|On mange à table.
+narrateur|Sa chaise ne bouge plus.
+papa|Tu poses les mains sur la table ?
+narrateur|Elle pose les mains.
+narrateur|La table est un peu chaude.
+maman|Tu as vu la petite fumée ?
+enfant-f|Elle monte encore.
+narrateur|La soupe sent les carottes.
+papa|On attend un petit moment.
+narrateur|Mila tient sa cuillère.
+narrateur|Elle reste assise.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>casserole,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Joséphine va manger. Que fait-elle ?</t>
+          <t>La soupe attend. Mila est où ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Joséphine va manger. Que fait-elle ?</t>
+          <t>narrateur|La soupe attend.
+narrateur|Mila est où ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Joséphine est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>Mila est assise. Elle est à table. On est tous assis. On est ensemble. La soupe attend. Ta chaise reste à table ? Oui. Mila reste assise. Le doudou écoute, tout sage. Il attend avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1731,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Joséphine est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>narrateur|Mila est assise.
+narrateur|Elle est à table.
+papa|On est tous assis.
+maman|On est ensemble.
+narrateur|La soupe attend.
+papa|Ta chaise reste à table ?
+enfant-f|Oui.
+narrateur|Mila reste assise.
+narrateur|Le doudou écoute, tout sage.
+maman|Il attend avec nous ?
+enfant-f|Oui.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Joséphine boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Mila prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est bon. Bravo, Mila. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Mila. Ils mangent ensemble. Mila reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Mila. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1910,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Joséphine boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+          <t>narrateur|Papa coupe le pain.
+narrateur|Le pain croustille.
+maman|Tu prends ta cuillère ?
+narrateur|Mila prend sa cuillère.
+papa|Tu attends un peu. C'est chaud.
+narrateur|Elle attend un peu.
+narrateur|Elle goûte.
+enfant-f|C'est chaud.
+enfant-f|C'est bon.
+maman|Bravo, Mila.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+papa|Bon appétit.
+maman|Bon appétit, Mila.
+narrateur|Ils mangent ensemble.
+narrateur|Mila reste assise.
+papa|Encore une petite cuillère ?
+narrateur|Encore une cuillère.
+papa|Tu restes assise. Bravo.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+maman|Merci, Mila.
+narrateur|Elle boit une gorgée.
+narrateur|Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La fumée s'en va. La cuillère de bois se repose. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La fumée s'en va.
+narrateur|La cuillère de bois se repose.
+papa|On a mangé assis, ensemble.
+enfant-f|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est l'heure du souper. Joséphine est dans la cuisine. Maman pose les assiettes. Papa apporte la soupe. La soupe sent les carottes. Joséphine va s'asseoir. Elle pose les fesses sur la chaise. Elle est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Joséphine tient sa cuillère. Elle mange assise. La chaise est stable. Maman dit : on mange ensemble, à table. Joséphine sourit. Elle reste assise. Papa coupe le pain. Joséphine attend, assise. Ils sont ensemble à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, les lampadaires s'allument. La rue devient orange. Un chat passe sous la fenêtre. Dans la maison, ça sent la soupe. Une petite fumée monte. Elle va jusqu'à la vitre. La cuillère en bois tape la casserole. Toc. Toc. Mila vit ici, avec papa et maman. Son doudou attend sur une chaise. Le doudou a une oreille pliée. J'entends la cuillère ! Oui, Mila. La soupe est presque prête. Papa apporte les assiettes. Elles font un petit bruit. Le pain est dans le panier. Mila, viens. On va à table. Viens t'asseoir. Mila va vers sa chaise. Le carrelage est tiède, encore. Ça sent les carottes. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Mila. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. La table est un peu chaude. Tu as vu la petite fumée ? Elle monte encore. La soupe sent les carottes. On attend un petit moment. Mila tient sa cuillère. Elle reste assise.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Joséphine va manger. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe attend. Mila est où ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1562,6 @@
 narrateur|Mila est où ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Joséphine est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est assise. Elle est à table. On est tous assis. On est ensemble. La soupe attend. Ta chaise reste à table ? Oui. Mila reste assise. Le doudou écoute, tout sage. Il attend avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,7 +1744,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1770,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Mila prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est bon. Bravo, Mila. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Mila. Ils mangent ensemble. Mila reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Mila. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Mila prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est bon. Bravo, Mila. Tu as goûté. Bon appétit. Bon appétit, Mila. Ils mangent ensemble. Mila reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Mila. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Joséphine boit une gorgée. Elle reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e jusqu'à la fin. Merci, dit maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa coupe le pain. Le pain croustille. Tu prends ta cuillère ? Mila prend sa cuillère. Tu attends un peu. C'est chaud. Elle attend un peu. Elle goûte. C'est chaud. C'est bon. Bravo, Mila. Tu as goûté. Bon appétit. Bon appétit, Mila. Ils mangent ensemble. Mila reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Mila. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1921,7 +1919,6 @@
 enfant-f|C'est bon.
 maman|Bravo, Mila.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 papa|Bon appétit.
 maman|Bon appétit, Mila.
 narrateur|Ils mangent ensemble.
@@ -1936,7 +1933,6 @@
 narrateur|Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. La cuillère de bois se repose. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La fumée s'en va. La cuillère de bois se repose. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fumée s'en va. La cuillère de bois se repose. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,12 +2101,9 @@
 narrateur|La cuillère de bois se repose.
 papa|On a mangé assis, ensemble.
 enfant-f|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Joséphine, maman, papa</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
